--- a/data/trans_orig/P1420-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1420-Edad-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hemorroides en 2012</t>
+          <t>Población con diagnóstico de hemorroides en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,97 +731,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4420</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>888</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4942</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4436</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>888</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5039</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>454146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>425288</t>
+          <t>425810</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>879337</t>
+          <t>879940</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9123</t>
+          <t>8890</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>7522</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12564</t>
+          <t>12633</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>677964</t>
+          <t>678197</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>686057</t>
+          <t>686061</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>603608</t>
+          <t>602733</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1284778</t>
+          <t>1284709</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1294604</t>
+          <t>1295273</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4235</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10947</t>
+          <t>11886</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12753</t>
+          <t>12067</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>677628</t>
+          <t>676627</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>698627</t>
+          <t>697688</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>707625</t>
+          <t>707647</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1378684</t>
+          <t>1379370</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1388550</t>
+          <t>1389430</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9479</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5480</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19514</t>
+          <t>19488</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7742</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23286</t>
+          <t>22921</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>605138</t>
+          <t>605859</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>613576</t>
+          <t>613580</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>594750</t>
+          <t>594776</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>608866</t>
+          <t>608784</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1205594</t>
+          <t>1205959</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1221256</t>
+          <t>1221138</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18999</t>
+          <t>18204</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7966</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23643</t>
+          <t>23422</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15943</t>
+          <t>16119</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36135</t>
+          <t>36491</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>410430</t>
+          <t>411225</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>424304</t>
+          <t>424052</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>424157</t>
+          <t>424378</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>439834</t>
+          <t>439829</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>841094</t>
+          <t>840738</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>861286</t>
+          <t>861110</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,16%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>10789</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>4878</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16683</t>
+          <t>17199</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24855</t>
+          <t>23842</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>298377</t>
+          <t>298997</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>307843</t>
+          <t>307921</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>337313</t>
+          <t>336797</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>349141</t>
+          <t>349118</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>638927</t>
+          <t>639940</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>654867</t>
+          <t>654905</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9891</t>
+          <t>9061</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7560</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23381</t>
+          <t>23470</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9825</t>
+          <t>9431</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25905</t>
+          <t>26618</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>239960</t>
+          <t>240790</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>365598</t>
+          <t>365509</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>381419</t>
+          <t>382237</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>612925</t>
+          <t>612212</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>629005</t>
+          <t>629399</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17734</t>
+          <t>18652</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38493</t>
+          <t>39174</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43503</t>
+          <t>43188</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74520</t>
+          <t>72167</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>66031</t>
+          <t>65040</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>102753</t>
+          <t>101819</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3388286</t>
+          <t>3387605</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3409045</t>
+          <t>3408127</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3480578</t>
+          <t>3482931</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3511595</t>
+          <t>3511910</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6879124</t>
+          <t>6880058</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6915846</t>
+          <t>6916837</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hemorroides en 2016</t>
+          <t>Población con diagnóstico de hemorroides en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3710,82 +3710,82 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5988</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>996</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4971</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>996</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>390784</t>
+          <t>389767</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>810265</t>
+          <t>810218</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4679</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>6979</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,6%</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>585817</t>
+          <t>585424</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>558616</t>
+          <t>558658</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1147992</t>
+          <t>1147061</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1900</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12959</t>
+          <t>12294</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>14543</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>656138</t>
+          <t>656803</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667197</t>
+          <t>667196</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>656046</t>
+          <t>656270</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1316067</t>
+          <t>1315940</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1327649</t>
+          <t>1327593</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16925</t>
+          <t>16918</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4754,7 +4754,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14229</t>
+          <t>14866</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8532</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25193</t>
+          <t>26283</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>629123</t>
+          <t>629130</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>642732</t>
+          <t>642137</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>634848</t>
+          <t>634211</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>645949</t>
+          <t>645968</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1269932</t>
+          <t>1268842</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1286593</t>
+          <t>1286469</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21210</t>
+          <t>19591</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>10990</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30579</t>
+          <t>29822</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>17300</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43346</t>
+          <t>42651</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>456708</t>
+          <t>458327</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>473919</t>
+          <t>474554</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>466270</t>
+          <t>467027</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>485611</t>
+          <t>485859</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>931421</t>
+          <t>932116</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>956899</t>
+          <t>957467</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10990</t>
+          <t>10899</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17217</t>
+          <t>16561</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22342</t>
+          <t>23007</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>323340</t>
+          <t>323431</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332408</t>
+          <t>332501</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>360545</t>
+          <t>361201</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>372821</t>
+          <t>372843</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>689750</t>
+          <t>689085</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>704081</t>
+          <t>704050</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11247</t>
+          <t>11213</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2555</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16595</t>
+          <t>16597</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>6715</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22458</t>
+          <t>21447</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>245751</t>
+          <t>245785</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>254638</t>
+          <t>255212</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>383574</t>
+          <t>383572</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>397614</t>
+          <t>397450</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>634709</t>
+          <t>635720</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>650647</t>
+          <t>650452</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22376</t>
+          <t>22827</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49158</t>
+          <t>48388</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33183</t>
+          <t>33311</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>64010</t>
+          <t>60737</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>60726</t>
+          <t>63546</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>99935</t>
+          <t>102248</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3345192</t>
+          <t>3345962</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3371974</t>
+          <t>3371523</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3480532</t>
+          <t>3483805</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3511359</t>
+          <t>3511231</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6838957</t>
+          <t>6836644</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6878166</t>
+          <t>6875346</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6309,12 +6309,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1420-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1420-Edad-trans_orig.xlsx
@@ -771,7 +771,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4539</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>425810</t>
+          <t>425691</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>879940</t>
+          <t>879973</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8890</t>
+          <t>9037</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7522</t>
+          <t>7098</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12633</t>
+          <t>12547</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>678197</t>
+          <t>678050</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>686061</t>
+          <t>686073</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>602733</t>
+          <t>603157</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1284709</t>
+          <t>1284795</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1295273</t>
+          <t>1295286</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11886</t>
+          <t>10807</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12067</t>
+          <t>11742</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>676627</t>
+          <t>676915</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>697688</t>
+          <t>698767</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>707647</t>
+          <t>707624</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1379370</t>
+          <t>1379695</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1389430</t>
+          <t>1389453</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8758</t>
+          <t>8868</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>5386</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19488</t>
+          <t>19600</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7742</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22921</t>
+          <t>23241</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>605859</t>
+          <t>605749</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>613580</t>
+          <t>614617</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>594776</t>
+          <t>594664</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>608784</t>
+          <t>608878</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1205959</t>
+          <t>1205639</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1221138</t>
+          <t>1221279</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5377</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18204</t>
+          <t>18486</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23422</t>
+          <t>23162</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16119</t>
+          <t>15138</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36491</t>
+          <t>36146</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>411225</t>
+          <t>410943</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>424052</t>
+          <t>424230</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>424378</t>
+          <t>424638</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>439829</t>
+          <t>439833</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>840738</t>
+          <t>841083</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>861110</t>
+          <t>862091</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10789</t>
+          <t>12462</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17199</t>
+          <t>16686</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>8620</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23842</t>
+          <t>23028</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>298997</t>
+          <t>297324</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>307921</t>
+          <t>307793</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>336797</t>
+          <t>337310</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>349118</t>
+          <t>349104</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>639940</t>
+          <t>640754</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>654905</t>
+          <t>655162</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9061</t>
+          <t>8900</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>24009</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9431</t>
+          <t>9734</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>26618</t>
+          <t>25743</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>240790</t>
+          <t>240951</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>248829</t>
+          <t>248832</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>365509</t>
+          <t>364970</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>382237</t>
+          <t>381263</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>612212</t>
+          <t>613087</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>629399</t>
+          <t>629096</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18652</t>
+          <t>18157</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39174</t>
+          <t>40208</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43188</t>
+          <t>42142</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72167</t>
+          <t>73299</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>65040</t>
+          <t>66054</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>101819</t>
+          <t>104383</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3387605</t>
+          <t>3386571</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3408127</t>
+          <t>3408622</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3482931</t>
+          <t>3481799</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3511910</t>
+          <t>3512956</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6880058</t>
+          <t>6877494</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6916837</t>
+          <t>6915823</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3765,7 +3765,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>389767</t>
+          <t>390742</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>810218</t>
+          <t>809119</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5072</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>585424</t>
+          <t>584660</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>558658</t>
+          <t>558574</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1147061</t>
+          <t>1147980</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12294</t>
+          <t>11913</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>4858</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14543</t>
+          <t>13770</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>656803</t>
+          <t>657184</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667196</t>
+          <t>667205</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>656270</t>
+          <t>656528</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1315940</t>
+          <t>1316713</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1327593</t>
+          <t>1327653</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16918</t>
+          <t>16687</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14866</t>
+          <t>14848</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26283</t>
+          <t>26585</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>629130</t>
+          <t>629361</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>642137</t>
+          <t>642658</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>634211</t>
+          <t>634229</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>645968</t>
+          <t>645913</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1268842</t>
+          <t>1268540</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1286469</t>
+          <t>1286451</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19591</t>
+          <t>18956</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10990</t>
+          <t>11457</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29822</t>
+          <t>32029</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17300</t>
+          <t>18183</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42651</t>
+          <t>40660</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>458327</t>
+          <t>458962</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>474554</t>
+          <t>474865</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>467027</t>
+          <t>464820</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>485859</t>
+          <t>485392</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>932116</t>
+          <t>934107</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>957467</t>
+          <t>956584</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1829</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10899</t>
+          <t>10674</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>4098</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16561</t>
+          <t>16573</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23007</t>
+          <t>22110</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>323431</t>
+          <t>323656</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>332501</t>
+          <t>332415</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>361201</t>
+          <t>361189</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>372843</t>
+          <t>373664</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>689085</t>
+          <t>689982</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>704050</t>
+          <t>704036</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11213</t>
+          <t>10717</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5783,12 +5783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16597</t>
+          <t>15207</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21447</t>
+          <t>22275</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -5881,12 +5881,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>245785</t>
+          <t>246281</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>255212</t>
+          <t>255213</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5896,12 +5896,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>383572</t>
+          <t>384962</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>397450</t>
+          <t>397633</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>635720</t>
+          <t>634892</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>650452</t>
+          <t>650412</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5966,12 +5966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22827</t>
+          <t>23115</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48388</t>
+          <t>48829</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>33311</t>
+          <t>33634</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60737</t>
+          <t>63069</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>63546</t>
+          <t>61837</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>102248</t>
+          <t>98423</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -6224,12 +6224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3345962</t>
+          <t>3345521</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3371523</t>
+          <t>3371235</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3483805</t>
+          <t>3481473</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3511231</t>
+          <t>3510908</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6836644</t>
+          <t>6840469</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6875346</t>
+          <t>6877055</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6309,12 +6309,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
